--- a/testakten/erbstreit-krypto-multisig-edelmann-stuttgart/xlsx/pflichtteilsberechnung_henrike_marie_theres.xlsx
+++ b/testakten/erbstreit-krypto-multisig-edelmann-stuttgart/xlsx/pflichtteilsberechnung_henrike_marie_theres.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H28"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -521,6 +521,7 @@
     <col width="25" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -535,10 +536,11 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1. REINNACHLASS (§ 2311 BGB)</t>
+          <t>1. REINNACHLASS (Paragraf 2311 BGB)</t>
         </is>
       </c>
     </row>
@@ -570,7 +572,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>SV Bender &amp; Moerser 02.05.2025</t>
+          <t>SV Bender &amp; Mörser 02.05.2025</t>
         </is>
       </c>
     </row>
@@ -646,10 +648,11 @@
       </c>
       <c r="D12" s="9" t="inlineStr"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2. ERGÄNZUNGSNACHLASS (§ 2325 BGB) — SCHENKUNGEN</t>
+          <t>2. ERGÄNZUNGSNACHLASS (Paragraf 2325 BGB) — SCHENKUNGEN</t>
         </is>
       </c>
     </row>
@@ -835,6 +838,7 @@
       <c r="F21" s="9" t="inlineStr"/>
       <c r="G21" s="9" t="inlineStr"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -968,7 +972,7 @@
       <c r="G27" s="10" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Ausgeschlagen (fragl. wirksam); Ergänzungspflicht § 2329 BGB</t>
+          <t>Ausgeschlagen (fragl. wirksam); Ergänzungspflicht Paragraf 2329 BGB</t>
         </is>
       </c>
     </row>
